--- a/server/apps/cmdb/support-files/model_config.xlsx
+++ b/server/apps/cmdb/support-files/model_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="15560" tabRatio="896" firstSheet="1" activeTab="2"/>
+    <workbookView windowHeight="15820" tabRatio="896" firstSheet="44" activeTab="55"/>
   </bookViews>
   <sheets>
     <sheet name="classifications" sheetId="1" r:id="rId1"/>
@@ -4718,7 +4718,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{91E54E81-F66B-8B5F-84B8-BC69EF198934}">
+    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{E6120DDA-9689-DF0F-7827-CF69B0055B5F}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
